--- a/analisis_vtc.xlsx
+++ b/analisis_vtc.xlsx
@@ -1430,7 +1430,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Datos reales del conductor, anonimizados (sin pasajeros, matrículas ni direcciones).</t>
+          <t>Datos reales de viajes, anonimizados (sin pasajeros, matrículas ni direcciones).</t>
         </is>
       </c>
     </row>
